--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MICHIGAN_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MICHIGAN_2013.xlsx
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C137">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C498">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C861">
